--- a/backend/data/financials_by_company/14D.AX.xlsx
+++ b/backend/data/financials_by_company/14D.AX.xlsx
@@ -672,7 +672,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -681,130 +681,132 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-2436711</v>
+        <v>-2800117</v>
       </c>
       <c r="E2" t="n">
-        <v>6982</v>
+        <v>-2933040</v>
       </c>
       <c r="F2" t="n">
-        <v>6982</v>
+        <v>-2933040</v>
       </c>
       <c r="G2" t="n">
-        <v>-2505500</v>
+        <v>-5974178</v>
       </c>
       <c r="H2" t="n">
-        <v>35242</v>
+        <v>136772</v>
       </c>
       <c r="I2" t="n">
-        <v>-2429729</v>
+        <v>-5733157</v>
       </c>
       <c r="J2" t="n">
-        <v>-2464971</v>
+        <v>-5869929</v>
       </c>
       <c r="K2" t="n">
-        <v>-10703</v>
+        <v>-85421</v>
       </c>
       <c r="L2" t="n">
-        <v>40529</v>
+        <v>104249</v>
       </c>
       <c r="M2" t="n">
-        <v>29826</v>
+        <v>18828</v>
       </c>
       <c r="N2" t="n">
-        <v>-2512482</v>
+        <v>-3041138</v>
       </c>
       <c r="O2" t="n">
-        <v>-2505500</v>
+        <v>-5974178</v>
       </c>
       <c r="P2" t="n">
-        <v>233614324</v>
+        <v>198566315</v>
       </c>
       <c r="Q2" t="n">
-        <v>233614324</v>
+        <v>198566315</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.0107</v>
+        <v>-0.030063</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0107</v>
+        <v>-0.030063</v>
       </c>
       <c r="T2" t="n">
-        <v>-2505500</v>
+        <v>-5974178</v>
       </c>
       <c r="U2" t="n">
-        <v>-2505500</v>
+        <v>-5974178</v>
       </c>
       <c r="V2" t="n">
-        <v>-2505500</v>
+        <v>-5974178</v>
       </c>
       <c r="W2" t="n">
-        <v>-2505500</v>
+        <v>-5974178</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-2505500</v>
+        <v>-5974178</v>
       </c>
       <c r="Z2" t="n">
-        <v>-405378</v>
+        <v>-2465315</v>
       </c>
       <c r="AA2" t="n">
-        <v>-69789</v>
+        <v>467725</v>
       </c>
       <c r="AB2" t="n">
-        <v>6982</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>6982</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>-342571</v>
-      </c>
+        <v>-2933040</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>2933040</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>-10703</v>
+        <v>-85421</v>
       </c>
       <c r="AG2" t="n">
-        <v>40529</v>
+        <v>104249</v>
       </c>
       <c r="AH2" t="n">
-        <v>29826</v>
+        <v>18828</v>
       </c>
       <c r="AI2" t="n">
-        <v>-2089419</v>
+        <v>-3423442</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2089419</v>
+        <v>3423442</v>
       </c>
       <c r="AK2" t="n">
-        <v>455974</v>
+        <v>297837</v>
       </c>
       <c r="AL2" t="n">
-        <v>35242</v>
+        <v>136772</v>
       </c>
       <c r="AM2" t="n">
-        <v>35242</v>
+        <v>136772</v>
       </c>
       <c r="AN2" t="n">
-        <v>35242</v>
-      </c>
-      <c r="AO2" t="inlineStr"/>
+        <v>136772</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6553</v>
+      </c>
       <c r="AP2" t="n">
-        <v>1598203</v>
+        <v>2982280</v>
       </c>
       <c r="AQ2" t="n">
-        <v>135562</v>
+        <v>50851</v>
       </c>
       <c r="AR2" t="n">
-        <v>1462641</v>
+        <v>2931429</v>
       </c>
       <c r="AS2" t="n">
-        <v>1282421</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
+        <v>1319515</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>73739</v>
+      </c>
       <c r="AU2" t="n">
-        <v>180220</v>
+        <v>1538175</v>
       </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr"/>
@@ -812,7 +814,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -821,130 +823,144 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-1800029</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+        <v>286082</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-997516</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-997516</v>
+      </c>
       <c r="G3" t="n">
-        <v>-1831251</v>
+        <v>-1369310</v>
       </c>
       <c r="H3" t="n">
-        <v>30200</v>
+        <v>380879</v>
       </c>
       <c r="I3" t="n">
-        <v>-1800029</v>
+        <v>-711434</v>
       </c>
       <c r="J3" t="n">
-        <v>-1830229</v>
+        <v>-1092313</v>
       </c>
       <c r="K3" t="n">
-        <v>28268</v>
+        <v>-257996</v>
       </c>
       <c r="L3" t="n">
-        <v>1022</v>
+        <v>276997</v>
       </c>
       <c r="M3" t="n">
-        <v>29290</v>
+        <v>19001</v>
       </c>
       <c r="N3" t="n">
-        <v>-1831251</v>
+        <v>-371794</v>
       </c>
       <c r="O3" t="n">
-        <v>-1831251</v>
+        <v>-1369310</v>
       </c>
       <c r="P3" t="n">
-        <v>208232358</v>
+        <v>207898277</v>
       </c>
       <c r="Q3" t="n">
-        <v>208232358</v>
+        <v>207898277</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.008796999999999999</v>
+        <v>-0.006573</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.008796999999999999</v>
+        <v>-0.006573</v>
       </c>
       <c r="T3" t="n">
-        <v>-1831251</v>
+        <v>-1369310</v>
       </c>
       <c r="U3" t="n">
-        <v>-1831251</v>
+        <v>-1369310</v>
       </c>
       <c r="V3" t="n">
-        <v>-1831251</v>
+        <v>-1369310</v>
       </c>
       <c r="W3" t="n">
-        <v>-1831251</v>
+        <v>-1369310</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1831251</v>
+        <v>-1369310</v>
       </c>
       <c r="Z3" t="n">
-        <v>-289392</v>
+        <v>2452841</v>
       </c>
       <c r="AA3" t="n">
-        <v>86096</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>3450357</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>-997516</v>
+      </c>
       <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="n">
-        <v>-375488</v>
-      </c>
+      <c r="AD3" t="n">
+        <v>997516</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>28268</v>
+        <v>-257996</v>
       </c>
       <c r="AG3" t="n">
-        <v>1022</v>
+        <v>276997</v>
       </c>
       <c r="AH3" t="n">
-        <v>29290</v>
+        <v>19001</v>
       </c>
       <c r="AI3" t="n">
-        <v>-1570127</v>
+        <v>-3564155</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1570127</v>
+        <v>3955064</v>
       </c>
       <c r="AK3" t="n">
-        <v>-226771</v>
+        <v>194004</v>
       </c>
       <c r="AL3" t="n">
-        <v>30200</v>
+        <v>380879</v>
       </c>
       <c r="AM3" t="n">
-        <v>30200</v>
+        <v>380879</v>
       </c>
       <c r="AN3" t="n">
-        <v>30200</v>
+        <v>380879</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>1766698</v>
+        <v>3380181</v>
       </c>
       <c r="AQ3" t="n">
-        <v>129639</v>
+        <v>69541</v>
       </c>
       <c r="AR3" t="n">
-        <v>1637059</v>
+        <v>3310640</v>
       </c>
       <c r="AS3" t="n">
-        <v>1226067</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
+        <v>2096249</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1556</v>
+      </c>
       <c r="AU3" t="n">
-        <v>410992</v>
-      </c>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
+        <v>1212835</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>390909</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>390909</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>390909</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -953,144 +969,130 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>286082</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-997516</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-997516</v>
-      </c>
+        <v>-1800029</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-1369310</v>
+        <v>-1831251</v>
       </c>
       <c r="H4" t="n">
-        <v>380879</v>
+        <v>30200</v>
       </c>
       <c r="I4" t="n">
-        <v>-711434</v>
+        <v>-1800029</v>
       </c>
       <c r="J4" t="n">
-        <v>-1092313</v>
+        <v>-1830229</v>
       </c>
       <c r="K4" t="n">
-        <v>-257996</v>
+        <v>28268</v>
       </c>
       <c r="L4" t="n">
-        <v>276997</v>
+        <v>1022</v>
       </c>
       <c r="M4" t="n">
-        <v>19001</v>
+        <v>29290</v>
       </c>
       <c r="N4" t="n">
-        <v>-371794</v>
+        <v>-1831251</v>
       </c>
       <c r="O4" t="n">
-        <v>-1369310</v>
+        <v>-1831251</v>
       </c>
       <c r="P4" t="n">
-        <v>207898277</v>
+        <v>208232358</v>
       </c>
       <c r="Q4" t="n">
-        <v>207898277</v>
+        <v>208232358</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.006573</v>
+        <v>-0.008796999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.006573</v>
+        <v>-0.008796999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-1369310</v>
+        <v>-1831251</v>
       </c>
       <c r="U4" t="n">
-        <v>-1369310</v>
+        <v>-1831251</v>
       </c>
       <c r="V4" t="n">
-        <v>-1369310</v>
+        <v>-1831251</v>
       </c>
       <c r="W4" t="n">
-        <v>-1369310</v>
+        <v>-1831251</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1369310</v>
+        <v>-1831251</v>
       </c>
       <c r="Z4" t="n">
-        <v>2452841</v>
+        <v>-289392</v>
       </c>
       <c r="AA4" t="n">
-        <v>3450357</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-997516</v>
-      </c>
+        <v>86096</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="n">
-        <v>997516</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>-375488</v>
+      </c>
       <c r="AF4" t="n">
-        <v>-257996</v>
+        <v>28268</v>
       </c>
       <c r="AG4" t="n">
-        <v>276997</v>
+        <v>1022</v>
       </c>
       <c r="AH4" t="n">
-        <v>19001</v>
+        <v>29290</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3564155</v>
+        <v>-1570127</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3955064</v>
+        <v>1570127</v>
       </c>
       <c r="AK4" t="n">
-        <v>194004</v>
+        <v>-226771</v>
       </c>
       <c r="AL4" t="n">
-        <v>380879</v>
+        <v>30200</v>
       </c>
       <c r="AM4" t="n">
-        <v>380879</v>
+        <v>30200</v>
       </c>
       <c r="AN4" t="n">
-        <v>380879</v>
+        <v>30200</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="n">
-        <v>3380181</v>
+        <v>1766698</v>
       </c>
       <c r="AQ4" t="n">
-        <v>69541</v>
+        <v>129639</v>
       </c>
       <c r="AR4" t="n">
-        <v>3310640</v>
+        <v>1637059</v>
       </c>
       <c r="AS4" t="n">
-        <v>2096249</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1556</v>
-      </c>
+        <v>1226067</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
-        <v>1212835</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>390909</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>390909</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>390909</v>
-      </c>
+        <v>410992</v>
+      </c>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -1099,132 +1101,130 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-2800117</v>
+        <v>-2436711</v>
       </c>
       <c r="E5" t="n">
-        <v>-2933040</v>
+        <v>6982</v>
       </c>
       <c r="F5" t="n">
-        <v>-2933040</v>
+        <v>6982</v>
       </c>
       <c r="G5" t="n">
-        <v>-5974178</v>
+        <v>-2505500</v>
       </c>
       <c r="H5" t="n">
-        <v>136772</v>
+        <v>35242</v>
       </c>
       <c r="I5" t="n">
-        <v>-5733157</v>
+        <v>-2429729</v>
       </c>
       <c r="J5" t="n">
-        <v>-5869929</v>
+        <v>-2464971</v>
       </c>
       <c r="K5" t="n">
-        <v>-85421</v>
+        <v>-10703</v>
       </c>
       <c r="L5" t="n">
-        <v>104249</v>
+        <v>40529</v>
       </c>
       <c r="M5" t="n">
-        <v>18828</v>
+        <v>29826</v>
       </c>
       <c r="N5" t="n">
-        <v>-3041138</v>
+        <v>-2512482</v>
       </c>
       <c r="O5" t="n">
-        <v>-5974178</v>
+        <v>-2505500</v>
       </c>
       <c r="P5" t="n">
-        <v>198566315</v>
+        <v>233614324</v>
       </c>
       <c r="Q5" t="n">
-        <v>198566315</v>
+        <v>233614324</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.030063</v>
+        <v>-0.0107</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.030063</v>
+        <v>-0.0107</v>
       </c>
       <c r="T5" t="n">
-        <v>-5974178</v>
+        <v>-2505500</v>
       </c>
       <c r="U5" t="n">
-        <v>-5974178</v>
+        <v>-2505500</v>
       </c>
       <c r="V5" t="n">
-        <v>-5974178</v>
+        <v>-2505500</v>
       </c>
       <c r="W5" t="n">
-        <v>-5974178</v>
+        <v>-2505500</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-5974178</v>
+        <v>-2505500</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2465315</v>
+        <v>-405378</v>
       </c>
       <c r="AA5" t="n">
-        <v>467725</v>
+        <v>-69789</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2933040</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
-        <v>2933040</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>6982</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6982</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>-342571</v>
+      </c>
       <c r="AF5" t="n">
-        <v>-85421</v>
+        <v>-10703</v>
       </c>
       <c r="AG5" t="n">
-        <v>104249</v>
+        <v>40529</v>
       </c>
       <c r="AH5" t="n">
-        <v>18828</v>
+        <v>29826</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3423442</v>
+        <v>-2089419</v>
       </c>
       <c r="AJ5" t="n">
-        <v>3423442</v>
+        <v>2089419</v>
       </c>
       <c r="AK5" t="n">
-        <v>297837</v>
+        <v>455974</v>
       </c>
       <c r="AL5" t="n">
-        <v>136772</v>
+        <v>35242</v>
       </c>
       <c r="AM5" t="n">
-        <v>136772</v>
+        <v>35242</v>
       </c>
       <c r="AN5" t="n">
-        <v>136772</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>6553</v>
-      </c>
+        <v>35242</v>
+      </c>
+      <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="n">
-        <v>2982280</v>
+        <v>1598203</v>
       </c>
       <c r="AQ5" t="n">
-        <v>50851</v>
+        <v>135562</v>
       </c>
       <c r="AR5" t="n">
-        <v>2931429</v>
+        <v>1462641</v>
       </c>
       <c r="AS5" t="n">
-        <v>1319515</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>73739</v>
-      </c>
+        <v>1282421</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
-        <v>1538175</v>
+        <v>180220</v>
       </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr"/>
@@ -1528,656 +1528,656 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>238168521</v>
+        <v>207217715</v>
       </c>
       <c r="C2" t="n">
-        <v>238168521</v>
+        <v>207217715</v>
       </c>
       <c r="D2" t="n">
-        <v>854786</v>
+        <v>1570232</v>
       </c>
       <c r="E2" t="n">
-        <v>6385509</v>
+        <v>5867036</v>
       </c>
       <c r="F2" t="n">
-        <v>7496292</v>
+        <v>11528336</v>
       </c>
       <c r="G2" t="n">
-        <v>3576751</v>
+        <v>5922078</v>
       </c>
       <c r="H2" t="n">
-        <v>6385509</v>
+        <v>5867036</v>
       </c>
       <c r="I2" t="n">
-        <v>854786</v>
+        <v>1570232</v>
       </c>
       <c r="J2" t="n">
-        <v>7496292</v>
+        <v>11528336</v>
       </c>
       <c r="K2" t="n">
-        <v>7496292</v>
+        <v>11528336</v>
       </c>
       <c r="L2" t="n">
-        <v>7496292</v>
+        <v>11528336</v>
       </c>
       <c r="M2" t="n">
-        <v>7496292</v>
+        <v>11528336</v>
       </c>
       <c r="N2" t="n">
-        <v>2639</v>
+        <v>196904</v>
       </c>
       <c r="O2" t="n">
-        <v>2639</v>
+        <v>196904</v>
       </c>
       <c r="P2" t="n">
-        <v>-26841287</v>
+        <v>-21154997</v>
       </c>
       <c r="Q2" t="n">
-        <v>34334940</v>
+        <v>32486429</v>
       </c>
       <c r="R2" t="n">
-        <v>34334940</v>
+        <v>32486429</v>
       </c>
       <c r="S2" t="n">
-        <v>1895728</v>
+        <v>2288948</v>
       </c>
       <c r="T2" t="n">
-        <v>798245</v>
+        <v>1286304</v>
       </c>
       <c r="U2" t="n">
-        <v>23498</v>
+        <v>31072</v>
       </c>
       <c r="V2" t="n">
-        <v>23498</v>
+        <v>31072</v>
       </c>
       <c r="W2" t="n">
-        <v>704747</v>
+        <v>1255232</v>
       </c>
       <c r="X2" t="n">
-        <v>704747</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>70000</v>
-      </c>
+        <v>1255232</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>1097483</v>
+        <v>1002644</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="n">
-        <v>150039</v>
+        <v>315000</v>
       </c>
       <c r="AC2" t="n">
-        <v>150039</v>
+        <v>315000</v>
       </c>
       <c r="AD2" t="n">
-        <v>152677</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>34000</v>
-      </c>
+        <v>78825</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>760767</v>
+        <v>608819</v>
       </c>
       <c r="AG2" t="n">
-        <v>760767</v>
+        <v>608819</v>
       </c>
       <c r="AH2" t="n">
-        <v>269262</v>
+        <v>213686</v>
       </c>
       <c r="AI2" t="n">
-        <v>491505</v>
+        <v>395133</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9392020</v>
+        <v>14360958</v>
       </c>
       <c r="AK2" t="n">
-        <v>4717786</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>761525</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1781941</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1781941</v>
-      </c>
+        <v>7436236</v>
+      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>1110783</v>
+        <v>5661300</v>
       </c>
       <c r="AP2" t="n">
-        <v>1110783</v>
+        <v>5661300</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1063537</v>
+        <v>1774936</v>
       </c>
       <c r="AR2" t="n">
-        <v>-146078</v>
+        <v>-164672</v>
       </c>
       <c r="AS2" t="n">
-        <v>1209615</v>
+        <v>1939608</v>
       </c>
       <c r="AT2" t="n">
-        <v>1076702</v>
+        <v>1766174</v>
       </c>
       <c r="AU2" t="n">
-        <v>132913</v>
+        <v>173434</v>
       </c>
       <c r="AV2" t="n">
-        <v>4674234</v>
+        <v>6924722</v>
       </c>
       <c r="AW2" t="n">
-        <v>1172</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>153834</v>
-      </c>
+        <v>131721</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>2647499</v>
+        <v>1088044</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2482059</v>
+        <v>543674</v>
       </c>
       <c r="BA2" t="n">
-        <v>165440</v>
+        <v>544370</v>
       </c>
       <c r="BB2" t="n">
-        <v>1871729</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>164377</v>
-      </c>
+        <v>5704957</v>
+      </c>
+      <c r="BC2" t="inlineStr"/>
       <c r="BD2" t="n">
-        <v>1707352</v>
+        <v>5704957</v>
       </c>
       <c r="BE2" t="n">
-        <v>1707352</v>
+        <v>5704957</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>212571163</v>
+        <v>208950473</v>
       </c>
       <c r="C3" t="n">
-        <v>212571163</v>
+        <v>208950473</v>
       </c>
       <c r="D3" t="n">
-        <v>227357</v>
+        <v>437167</v>
       </c>
       <c r="E3" t="n">
-        <v>6472049</v>
+        <v>8652834</v>
       </c>
       <c r="F3" t="n">
-        <v>8834118</v>
+        <v>10475738</v>
       </c>
       <c r="G3" t="n">
-        <v>3734207</v>
+        <v>5920493</v>
       </c>
       <c r="H3" t="n">
-        <v>6472049</v>
+        <v>8652834</v>
       </c>
       <c r="I3" t="n">
-        <v>227357</v>
+        <v>437167</v>
       </c>
       <c r="J3" t="n">
-        <v>8834118</v>
+        <v>10475738</v>
       </c>
       <c r="K3" t="n">
-        <v>8834118</v>
+        <v>10475738</v>
       </c>
       <c r="L3" t="n">
-        <v>8834118</v>
+        <v>10475738</v>
       </c>
       <c r="M3" t="n">
-        <v>8834118</v>
+        <v>10475738</v>
       </c>
       <c r="N3" t="n">
-        <v>167720</v>
+        <v>323395</v>
       </c>
       <c r="O3" t="n">
-        <v>167720</v>
+        <v>323395</v>
       </c>
       <c r="P3" t="n">
-        <v>-24335787</v>
+        <v>-22504536</v>
       </c>
       <c r="Q3" t="n">
-        <v>33002185</v>
+        <v>32656879</v>
       </c>
       <c r="R3" t="n">
-        <v>33002185</v>
+        <v>32656879</v>
       </c>
       <c r="S3" t="n">
-        <v>893189</v>
+        <v>1515973</v>
       </c>
       <c r="T3" t="n">
-        <v>21457</v>
+        <v>307405</v>
       </c>
       <c r="U3" t="n">
-        <v>21457</v>
+        <v>75238</v>
       </c>
       <c r="V3" t="n">
-        <v>21457</v>
-      </c>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
+        <v>75238</v>
+      </c>
+      <c r="W3" t="n">
+        <v>232167</v>
+      </c>
+      <c r="X3" t="n">
+        <v>232167</v>
+      </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>871732</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>1208568</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>500000</v>
+      </c>
       <c r="AB3" t="n">
-        <v>227357</v>
+        <v>205000</v>
       </c>
       <c r="AC3" t="n">
-        <v>227357</v>
+        <v>205000</v>
       </c>
       <c r="AD3" t="n">
-        <v>124829</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>34000</v>
-      </c>
+        <v>58577</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>485546</v>
+        <v>444991</v>
       </c>
       <c r="AG3" t="n">
-        <v>485546</v>
+        <v>444991</v>
       </c>
       <c r="AH3" t="n">
-        <v>102971</v>
+        <v>89510</v>
       </c>
       <c r="AI3" t="n">
-        <v>382575</v>
+        <v>355481</v>
       </c>
       <c r="AJ3" t="n">
-        <v>9727307</v>
+        <v>11991711</v>
       </c>
       <c r="AK3" t="n">
-        <v>5121368</v>
+        <v>4862650</v>
       </c>
       <c r="AL3" t="n">
-        <v>360456</v>
+        <v>64075</v>
       </c>
       <c r="AM3" t="n">
-        <v>2124512</v>
+        <v>2500000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2124512</v>
+        <v>2500000</v>
       </c>
       <c r="AO3" t="n">
-        <v>2362069</v>
+        <v>1822904</v>
       </c>
       <c r="AP3" t="n">
-        <v>2362069</v>
+        <v>1822904</v>
       </c>
       <c r="AQ3" t="n">
-        <v>274331</v>
+        <v>475671</v>
       </c>
       <c r="AR3" t="n">
-        <v>-701834</v>
+        <v>-301602</v>
       </c>
       <c r="AS3" t="n">
-        <v>976165</v>
+        <v>777273</v>
       </c>
       <c r="AT3" t="n">
-        <v>901984</v>
+        <v>716307</v>
       </c>
       <c r="AU3" t="n">
-        <v>74181</v>
+        <v>60966</v>
       </c>
       <c r="AV3" t="n">
-        <v>4605939</v>
+        <v>7129061</v>
       </c>
       <c r="AW3" t="n">
-        <v>2688</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>169798</v>
-      </c>
+        <v>137021</v>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="n">
-        <v>2484996</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>2453790</v>
-      </c>
+        <v>3442624</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>31206</v>
+        <v>3442624</v>
       </c>
       <c r="BB3" t="n">
-        <v>1948457</v>
+        <v>3549416</v>
       </c>
       <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="n">
-        <v>1948457</v>
+        <v>3549416</v>
       </c>
       <c r="BE3" t="n">
-        <v>1948457</v>
+        <v>3549416</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>208950473</v>
+        <v>212571163</v>
       </c>
       <c r="C4" t="n">
-        <v>208950473</v>
+        <v>212571163</v>
       </c>
       <c r="D4" t="n">
-        <v>437167</v>
+        <v>227357</v>
       </c>
       <c r="E4" t="n">
-        <v>8652834</v>
+        <v>6472049</v>
       </c>
       <c r="F4" t="n">
-        <v>10475738</v>
+        <v>8834118</v>
       </c>
       <c r="G4" t="n">
-        <v>5920493</v>
+        <v>3734207</v>
       </c>
       <c r="H4" t="n">
-        <v>8652834</v>
+        <v>6472049</v>
       </c>
       <c r="I4" t="n">
-        <v>437167</v>
+        <v>227357</v>
       </c>
       <c r="J4" t="n">
-        <v>10475738</v>
+        <v>8834118</v>
       </c>
       <c r="K4" t="n">
-        <v>10475738</v>
+        <v>8834118</v>
       </c>
       <c r="L4" t="n">
-        <v>10475738</v>
+        <v>8834118</v>
       </c>
       <c r="M4" t="n">
-        <v>10475738</v>
+        <v>8834118</v>
       </c>
       <c r="N4" t="n">
-        <v>323395</v>
+        <v>167720</v>
       </c>
       <c r="O4" t="n">
-        <v>323395</v>
+        <v>167720</v>
       </c>
       <c r="P4" t="n">
-        <v>-22504536</v>
+        <v>-24335787</v>
       </c>
       <c r="Q4" t="n">
-        <v>32656879</v>
+        <v>33002185</v>
       </c>
       <c r="R4" t="n">
-        <v>32656879</v>
+        <v>33002185</v>
       </c>
       <c r="S4" t="n">
-        <v>1515973</v>
+        <v>893189</v>
       </c>
       <c r="T4" t="n">
-        <v>307405</v>
+        <v>21457</v>
       </c>
       <c r="U4" t="n">
-        <v>75238</v>
+        <v>21457</v>
       </c>
       <c r="V4" t="n">
-        <v>75238</v>
-      </c>
-      <c r="W4" t="n">
-        <v>232167</v>
-      </c>
-      <c r="X4" t="n">
-        <v>232167</v>
-      </c>
+        <v>21457</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>1208568</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>500000</v>
-      </c>
+        <v>871732</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>205000</v>
+        <v>227357</v>
       </c>
       <c r="AC4" t="n">
-        <v>205000</v>
+        <v>227357</v>
       </c>
       <c r="AD4" t="n">
-        <v>58577</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>124829</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>34000</v>
+      </c>
       <c r="AF4" t="n">
-        <v>444991</v>
+        <v>485546</v>
       </c>
       <c r="AG4" t="n">
-        <v>444991</v>
+        <v>485546</v>
       </c>
       <c r="AH4" t="n">
-        <v>89510</v>
+        <v>102971</v>
       </c>
       <c r="AI4" t="n">
-        <v>355481</v>
+        <v>382575</v>
       </c>
       <c r="AJ4" t="n">
-        <v>11991711</v>
+        <v>9727307</v>
       </c>
       <c r="AK4" t="n">
-        <v>4862650</v>
+        <v>5121368</v>
       </c>
       <c r="AL4" t="n">
-        <v>64075</v>
+        <v>360456</v>
       </c>
       <c r="AM4" t="n">
-        <v>2500000</v>
+        <v>2124512</v>
       </c>
       <c r="AN4" t="n">
-        <v>2500000</v>
+        <v>2124512</v>
       </c>
       <c r="AO4" t="n">
-        <v>1822904</v>
+        <v>2362069</v>
       </c>
       <c r="AP4" t="n">
-        <v>1822904</v>
+        <v>2362069</v>
       </c>
       <c r="AQ4" t="n">
-        <v>475671</v>
+        <v>274331</v>
       </c>
       <c r="AR4" t="n">
-        <v>-301602</v>
+        <v>-701834</v>
       </c>
       <c r="AS4" t="n">
-        <v>777273</v>
+        <v>976165</v>
       </c>
       <c r="AT4" t="n">
-        <v>716307</v>
+        <v>901984</v>
       </c>
       <c r="AU4" t="n">
-        <v>60966</v>
+        <v>74181</v>
       </c>
       <c r="AV4" t="n">
-        <v>7129061</v>
+        <v>4605939</v>
       </c>
       <c r="AW4" t="n">
-        <v>137021</v>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+        <v>2688</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>169798</v>
+      </c>
       <c r="AY4" t="n">
-        <v>3442624</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
+        <v>2484996</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2453790</v>
+      </c>
       <c r="BA4" t="n">
-        <v>3442624</v>
+        <v>31206</v>
       </c>
       <c r="BB4" t="n">
-        <v>3549416</v>
+        <v>1948457</v>
       </c>
       <c r="BC4" t="inlineStr"/>
       <c r="BD4" t="n">
-        <v>3549416</v>
+        <v>1948457</v>
       </c>
       <c r="BE4" t="n">
-        <v>3549416</v>
+        <v>1948457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>207217715</v>
+        <v>238168521</v>
       </c>
       <c r="C5" t="n">
-        <v>207217715</v>
+        <v>238168521</v>
       </c>
       <c r="D5" t="n">
-        <v>1570232</v>
+        <v>854786</v>
       </c>
       <c r="E5" t="n">
-        <v>5867036</v>
+        <v>6385509</v>
       </c>
       <c r="F5" t="n">
-        <v>11528336</v>
+        <v>7496292</v>
       </c>
       <c r="G5" t="n">
-        <v>5922078</v>
+        <v>3576751</v>
       </c>
       <c r="H5" t="n">
-        <v>5867036</v>
+        <v>6385509</v>
       </c>
       <c r="I5" t="n">
-        <v>1570232</v>
+        <v>854786</v>
       </c>
       <c r="J5" t="n">
-        <v>11528336</v>
+        <v>7496292</v>
       </c>
       <c r="K5" t="n">
-        <v>11528336</v>
+        <v>7496292</v>
       </c>
       <c r="L5" t="n">
-        <v>11528336</v>
+        <v>7496292</v>
       </c>
       <c r="M5" t="n">
-        <v>11528336</v>
+        <v>7496292</v>
       </c>
       <c r="N5" t="n">
-        <v>196904</v>
+        <v>2639</v>
       </c>
       <c r="O5" t="n">
-        <v>196904</v>
+        <v>2639</v>
       </c>
       <c r="P5" t="n">
-        <v>-21154997</v>
+        <v>-26841287</v>
       </c>
       <c r="Q5" t="n">
-        <v>32486429</v>
+        <v>34334940</v>
       </c>
       <c r="R5" t="n">
-        <v>32486429</v>
+        <v>34334940</v>
       </c>
       <c r="S5" t="n">
-        <v>2288948</v>
+        <v>1895728</v>
       </c>
       <c r="T5" t="n">
-        <v>1286304</v>
+        <v>798245</v>
       </c>
       <c r="U5" t="n">
-        <v>31072</v>
+        <v>23498</v>
       </c>
       <c r="V5" t="n">
-        <v>31072</v>
+        <v>23498</v>
       </c>
       <c r="W5" t="n">
-        <v>1255232</v>
+        <v>704747</v>
       </c>
       <c r="X5" t="n">
-        <v>1255232</v>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+        <v>704747</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>70000</v>
+      </c>
       <c r="Z5" t="n">
-        <v>1002644</v>
+        <v>1097483</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>315000</v>
+        <v>150039</v>
       </c>
       <c r="AC5" t="n">
-        <v>315000</v>
+        <v>150039</v>
       </c>
       <c r="AD5" t="n">
-        <v>78825</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>152677</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>34000</v>
+      </c>
       <c r="AF5" t="n">
-        <v>608819</v>
+        <v>760767</v>
       </c>
       <c r="AG5" t="n">
-        <v>608819</v>
+        <v>760767</v>
       </c>
       <c r="AH5" t="n">
-        <v>213686</v>
+        <v>269262</v>
       </c>
       <c r="AI5" t="n">
-        <v>395133</v>
+        <v>491505</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14360958</v>
+        <v>9392020</v>
       </c>
       <c r="AK5" t="n">
-        <v>7436236</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>4717786</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>761525</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1781941</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1781941</v>
+      </c>
       <c r="AO5" t="n">
-        <v>5661300</v>
+        <v>1110783</v>
       </c>
       <c r="AP5" t="n">
-        <v>5661300</v>
+        <v>1110783</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1774936</v>
+        <v>1063537</v>
       </c>
       <c r="AR5" t="n">
-        <v>-164672</v>
+        <v>-146078</v>
       </c>
       <c r="AS5" t="n">
-        <v>1939608</v>
+        <v>1209615</v>
       </c>
       <c r="AT5" t="n">
-        <v>1766174</v>
+        <v>1076702</v>
       </c>
       <c r="AU5" t="n">
-        <v>173434</v>
+        <v>132913</v>
       </c>
       <c r="AV5" t="n">
-        <v>6924722</v>
+        <v>4674234</v>
       </c>
       <c r="AW5" t="n">
-        <v>131721</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>1172</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>153834</v>
+      </c>
       <c r="AY5" t="n">
-        <v>1088044</v>
+        <v>2647499</v>
       </c>
       <c r="AZ5" t="n">
-        <v>543674</v>
+        <v>2482059</v>
       </c>
       <c r="BA5" t="n">
-        <v>544370</v>
+        <v>165440</v>
       </c>
       <c r="BB5" t="n">
-        <v>5704957</v>
-      </c>
-      <c r="BC5" t="inlineStr"/>
+        <v>1871729</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>164377</v>
+      </c>
       <c r="BD5" t="n">
-        <v>5704957</v>
+        <v>1707352</v>
       </c>
       <c r="BE5" t="n">
-        <v>5704957</v>
+        <v>1707352</v>
       </c>
     </row>
   </sheetData>
@@ -2373,386 +2373,386 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-2519318</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-137984</v>
-      </c>
+        <v>-2393455</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>1470739</v>
+        <v>3175540</v>
       </c>
       <c r="E2" t="n">
-        <v>-424474</v>
+        <v>-1383681</v>
       </c>
       <c r="F2" t="n">
-        <v>40529</v>
+        <v>42637</v>
       </c>
       <c r="G2" t="n">
-        <v>1707352</v>
+        <v>5704957</v>
       </c>
       <c r="H2" t="n">
-        <v>1948457</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>4395479</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-274</v>
+      </c>
       <c r="J2" t="n">
-        <v>-241105</v>
+        <v>1309752</v>
       </c>
       <c r="K2" t="n">
-        <v>1071556</v>
+        <v>3116048</v>
       </c>
       <c r="L2" t="n">
-        <v>1071556</v>
+        <v>3116048</v>
       </c>
       <c r="M2" t="n">
-        <v>-522398</v>
+        <v>-59492</v>
       </c>
       <c r="N2" t="n">
-        <v>1332755</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-137984</v>
-      </c>
+        <v>3175540</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1470739</v>
+        <v>3175540</v>
       </c>
       <c r="Q2" t="n">
-        <v>782183</v>
+        <v>587159</v>
       </c>
       <c r="R2" t="n">
-        <v>782183</v>
+        <v>587159</v>
       </c>
       <c r="S2" t="n">
-        <v>299675</v>
-      </c>
-      <c r="T2" t="n">
-        <v>900000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>900000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>16000</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>-1376133</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-1376133</v>
+      </c>
       <c r="X2" t="n">
-        <v>-135457</v>
+        <v>-7548</v>
       </c>
       <c r="Y2" t="n">
-        <v>6982</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-142439</v>
-      </c>
+        <v>-7548</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>-282035</v>
+        <v>1954840</v>
       </c>
       <c r="AB2" t="n">
-        <v>-2094844</v>
+        <v>-2393455</v>
       </c>
       <c r="AC2" t="n">
-        <v>29826</v>
+        <v>18398</v>
       </c>
       <c r="AD2" t="n">
-        <v>-40529</v>
+        <v>-42637</v>
       </c>
       <c r="AE2" t="n">
-        <v>-2120252</v>
+        <v>-2912441</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2120252</v>
+        <v>-2912441</v>
       </c>
       <c r="AG2" t="n">
-        <v>36111</v>
+        <v>543225</v>
       </c>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>492250</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>36111</v>
+        <v>50975</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-7869789</v>
+        <v>-3914610</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>276806</v>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>-5858989</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1022</v>
-      </c>
+        <v>-1477472</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>1948457</v>
+        <v>3549416</v>
       </c>
       <c r="H3" t="n">
-        <v>3549416</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>5704957</v>
+      </c>
+      <c r="I3" t="n">
+        <v>44</v>
+      </c>
       <c r="J3" t="n">
-        <v>-1600959</v>
+        <v>-2155585</v>
       </c>
       <c r="K3" t="n">
-        <v>21814</v>
+        <v>-350000</v>
       </c>
       <c r="L3" t="n">
-        <v>21814</v>
+        <v>-350000</v>
       </c>
       <c r="M3" t="n">
-        <v>-509984</v>
-      </c>
-      <c r="N3" t="n">
-        <v>276806</v>
-      </c>
+        <v>-700000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="n">
-        <v>276806</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>388027</v>
+        <v>631553</v>
       </c>
       <c r="R3" t="n">
-        <v>388027</v>
+        <v>631553</v>
       </c>
       <c r="S3" t="n">
-        <v>2422379</v>
-      </c>
-      <c r="T3" t="n">
-        <v>900000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>900000</v>
-      </c>
+        <v>2109025</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-2924637</v>
+        <v>-2259751</v>
       </c>
       <c r="W3" t="n">
-        <v>-2924637</v>
+        <v>-2259751</v>
       </c>
       <c r="X3" t="n">
-        <v>-9715</v>
+        <v>-47828</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-9715</v>
+        <v>-47828</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2924637</v>
+        <v>830107</v>
       </c>
       <c r="AB3" t="n">
-        <v>-2010800</v>
+        <v>-2437138</v>
       </c>
       <c r="AC3" t="n">
-        <v>29277</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-1022</v>
-      </c>
+        <v>19004</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-2069145</v>
+        <v>-3019385</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2069145</v>
+        <v>-3019385</v>
       </c>
       <c r="AG3" t="n">
-        <v>30090</v>
-      </c>
-      <c r="AH3" t="inlineStr"/>
+        <v>563243</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>390909</v>
+      </c>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>30090</v>
+        <v>172334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-3914610</v>
+        <v>-7869789</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>276806</v>
+      </c>
       <c r="E4" t="n">
-        <v>-1477472</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>-5858989</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1022</v>
+      </c>
       <c r="G4" t="n">
+        <v>1948457</v>
+      </c>
+      <c r="H4" t="n">
         <v>3549416</v>
       </c>
-      <c r="H4" t="n">
-        <v>5704957</v>
-      </c>
-      <c r="I4" t="n">
-        <v>44</v>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>-2155585</v>
+        <v>-1600959</v>
       </c>
       <c r="K4" t="n">
-        <v>-350000</v>
+        <v>21814</v>
       </c>
       <c r="L4" t="n">
-        <v>-350000</v>
+        <v>21814</v>
       </c>
       <c r="M4" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>-509984</v>
+      </c>
+      <c r="N4" t="n">
+        <v>276806</v>
+      </c>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+      <c r="P4" t="n">
+        <v>276806</v>
+      </c>
       <c r="Q4" t="n">
-        <v>631553</v>
+        <v>388027</v>
       </c>
       <c r="R4" t="n">
-        <v>631553</v>
+        <v>388027</v>
       </c>
       <c r="S4" t="n">
-        <v>2109025</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>2422379</v>
+      </c>
+      <c r="T4" t="n">
+        <v>900000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>900000</v>
+      </c>
       <c r="V4" t="n">
-        <v>-2259751</v>
+        <v>-2924637</v>
       </c>
       <c r="W4" t="n">
-        <v>-2259751</v>
+        <v>-2924637</v>
       </c>
       <c r="X4" t="n">
-        <v>-47828</v>
+        <v>-9715</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>-47828</v>
+        <v>-9715</v>
       </c>
       <c r="AA4" t="n">
-        <v>830107</v>
+        <v>-2924637</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2437138</v>
+        <v>-2010800</v>
       </c>
       <c r="AC4" t="n">
-        <v>19004</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>29277</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>-1022</v>
+      </c>
       <c r="AE4" t="n">
-        <v>-3019385</v>
+        <v>-2069145</v>
       </c>
       <c r="AF4" t="n">
-        <v>-3019385</v>
+        <v>-2069145</v>
       </c>
       <c r="AG4" t="n">
-        <v>563243</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>390909</v>
-      </c>
+        <v>30090</v>
+      </c>
+      <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>172334</v>
+        <v>30090</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-2393455</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>-2519318</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-137984</v>
+      </c>
       <c r="D5" t="n">
-        <v>3175540</v>
+        <v>1470739</v>
       </c>
       <c r="E5" t="n">
-        <v>-1383681</v>
+        <v>-424474</v>
       </c>
       <c r="F5" t="n">
-        <v>42637</v>
+        <v>40529</v>
       </c>
       <c r="G5" t="n">
-        <v>5704957</v>
+        <v>1707352</v>
       </c>
       <c r="H5" t="n">
-        <v>4395479</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-274</v>
-      </c>
+        <v>1948457</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>1309752</v>
+        <v>-241105</v>
       </c>
       <c r="K5" t="n">
-        <v>3116048</v>
+        <v>1071556</v>
       </c>
       <c r="L5" t="n">
-        <v>3116048</v>
+        <v>1071556</v>
       </c>
       <c r="M5" t="n">
-        <v>-59492</v>
+        <v>-522398</v>
       </c>
       <c r="N5" t="n">
-        <v>3175540</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>1332755</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-137984</v>
+      </c>
       <c r="P5" t="n">
-        <v>3175540</v>
+        <v>1470739</v>
       </c>
       <c r="Q5" t="n">
-        <v>587159</v>
+        <v>782183</v>
       </c>
       <c r="R5" t="n">
-        <v>587159</v>
+        <v>782183</v>
       </c>
       <c r="S5" t="n">
-        <v>16000</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="n">
-        <v>-1376133</v>
-      </c>
-      <c r="W5" t="n">
-        <v>-1376133</v>
-      </c>
+        <v>299675</v>
+      </c>
+      <c r="T5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>900000</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-7548</v>
+        <v>-135457</v>
       </c>
       <c r="Y5" t="n">
-        <v>-7548</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>6982</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-142439</v>
+      </c>
       <c r="AA5" t="n">
-        <v>1954840</v>
+        <v>-282035</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2393455</v>
+        <v>-2094844</v>
       </c>
       <c r="AC5" t="n">
-        <v>18398</v>
+        <v>29826</v>
       </c>
       <c r="AD5" t="n">
-        <v>-42637</v>
+        <v>-40529</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2912441</v>
+        <v>-2120252</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2912441</v>
+        <v>-2120252</v>
       </c>
       <c r="AG5" t="n">
-        <v>543225</v>
+        <v>36111</v>
       </c>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="n">
-        <v>492250</v>
-      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>50975</v>
+        <v>36111</v>
       </c>
     </row>
   </sheetData>
@@ -3267,187 +3267,187 @@
       </c>
       <c r="CV1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="EG1" t="inlineStr">
@@ -3552,55 +3552,55 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="V2" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="W2" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="X2" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.13</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0.12</v>
-      </c>
       <c r="Z2" t="n">
-        <v>0.125</v>
+        <v>0.11</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.099</v>
+        <v>0.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.13</v>
+        <v>0.115</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.9330000000000001</v>
+        <v>1.353</v>
       </c>
       <c r="AE2" t="n">
-        <v>16461185</v>
+        <v>19492567</v>
       </c>
       <c r="AF2" t="n">
-        <v>16461185</v>
+        <v>19492567</v>
       </c>
       <c r="AG2" t="n">
-        <v>21572600</v>
+        <v>30775654</v>
       </c>
       <c r="AH2" t="n">
-        <v>47955397</v>
+        <v>42496250</v>
       </c>
       <c r="AI2" t="n">
-        <v>47955397</v>
+        <v>42496250</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1</v>
+        <v>0.105</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.105</v>
+        <v>0.11</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -3609,10 +3609,10 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>60653324</v>
+        <v>64970392</v>
       </c>
       <c r="AO2" t="n">
-        <v>72783992</v>
+        <v>78935992</v>
       </c>
       <c r="AP2" t="n">
         <v>0.013</v>
@@ -3627,10 +3627,10 @@
         <v>0.013</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.04606</v>
+        <v>0.067</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.0324925</v>
+        <v>0.0375075</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>44531560</v>
+        <v>48252180</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
@@ -3656,22 +3656,22 @@
         <v>282402506</v>
       </c>
       <c r="BC2" t="n">
-        <v>606533273</v>
+        <v>607199940</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.14912</v>
+        <v>0.12517999</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.09186</v>
+        <v>0.07711999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>606533273</v>
+        <v>607199940</v>
       </c>
       <c r="BG2" t="n">
         <v>0.011</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.090909</v>
+        <v>9.727273</v>
       </c>
       <c r="BI2" t="n">
         <v>1751241600</v>
@@ -3689,13 +3689,13 @@
         <v>-0.02</v>
       </c>
       <c r="BN2" t="n">
-        <v>-7.934</v>
+        <v>-8.597</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.6666665</v>
+        <v>7.125</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="BR2" t="n">
-        <v>0.1</v>
+        <v>0.107</v>
       </c>
       <c r="BS2" t="n">
         <v>0.08500000000000001</v>
@@ -3808,140 +3808,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CV2" t="b">
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>ASX</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>finmb_550418331</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>Australia/Sydney</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>AEST</t>
+        </is>
+      </c>
+      <c r="CZ2" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>au_market</t>
+        </is>
+      </c>
+      <c r="DB2" t="b">
         <v>0</v>
       </c>
-      <c r="CW2" t="b">
+      <c r="DC2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.5970149</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.069492504</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.8527628</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DI2" t="b">
         <v>0</v>
       </c>
-      <c r="CX2" t="n">
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>1782175583</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>1414DEGREE FPO [14D]</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>1414 Degrees Limited</t>
+        </is>
+      </c>
+      <c r="DO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DP2" t="n">
         <v>1536710400000</v>
       </c>
-      <c r="CY2" t="n">
-        <v>-0.019999996</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>0.099 - 0.13</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>1414 Degrees Limited</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>-16.666662</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DF2" t="n">
-        <v>1780447925</v>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DQ2" t="n">
+        <v>-0.022999994</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>0.1 - 0.115</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
         <is>
           <t>ASX</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>finmb_550418331</t>
-        </is>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>Australia/Sydney</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>AEST</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>36000000</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>au_market</t>
-        </is>
-      </c>
-      <c r="DM2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>1414DEGREE FPO [14D]</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>ASX</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>21572600</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>6.6923075</v>
-      </c>
-      <c r="DS2" t="inlineStr">
+      <c r="DT2" t="n">
+        <v>30775654</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>7.2307687</v>
+      </c>
+      <c r="DW2" t="inlineStr">
         <is>
           <t>0.013 - 0.165</t>
         </is>
       </c>
-      <c r="DT2" t="n">
-        <v>-0.065000005</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.3939394</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>566.6666</v>
-      </c>
-      <c r="DW2" t="n">
+      <c r="DX2" t="n">
+        <v>-0.058000006</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.35151517</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>712.5</v>
+      </c>
+      <c r="EA2" t="n">
         <v>1753317785</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EB2" t="n">
         <v>1753663385</v>
       </c>
-      <c r="DY2" t="b">
+      <c r="EC2" t="b">
         <v>1</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="ED2" t="n">
         <v>-0.02</v>
       </c>
-      <c r="EA2" t="n">
-        <v>0.053940002</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1.1710813</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.067507505</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>2.0776334</v>
-      </c>
       <c r="EE2" t="n">
-        <v>20</v>
+        <v>-17.692305</v>
       </c>
       <c r="EF2" t="n">
-        <v>20</v>
+        <v>0.107</v>
       </c>
       <c r="EG2" t="inlineStr"/>
     </row>
